--- a/Result/profitability/9941.xlsx
+++ b/Result/profitability/9941.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>1.815</v>
+        <v>1.7225</v>
       </c>
       <c r="N2" t="n">
-        <v>42.61125</v>
+        <v>41.9275</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.57</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5375</v>
+        <v>1.60875</v>
       </c>
       <c r="N3" t="n">
-        <v>40.13125</v>
+        <v>39.89875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.48</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4125</v>
+        <v>1.42</v>
       </c>
       <c r="N4" t="n">
-        <v>38.1475</v>
+        <v>37.7325</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>1.21375</v>
+        <v>1.23</v>
       </c>
       <c r="N5" t="n">
-        <v>35.94375</v>
+        <v>35.85375000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.72</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06375</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>35.1025</v>
+        <v>34.84625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.87</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9125</v>
+        <v>0.93375</v>
       </c>
       <c r="N7" t="n">
-        <v>34.53125</v>
+        <v>34.53</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.83</v>
       </c>
       <c r="M8" t="n">
-        <v>0.78125</v>
+        <v>0.8099999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>34.3225</v>
+        <v>34.175</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>0.89</v>
       </c>
       <c r="M13" t="n">
-        <v>0.945</v>
+        <v>0.9450000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>39.67125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9941</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9962</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5729</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4233</v>
+      </c>
+      <c r="F75" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1498</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.04%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>44</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1542</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1237</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.00125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>44.31625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.2299999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.1263736263736261</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0270208381039615</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.1299999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.06770833333333326</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.7199999999999989</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.0166628095348299</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
